--- a/artfynd/A 4278-2024 artfynd.xlsx
+++ b/artfynd/A 4278-2024 artfynd.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 4278-2024 artfynd.xlsx
+++ b/artfynd/A 4278-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>119816408</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>119835399</v>
       </c>
       <c r="B6" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
